--- a/sample-uploads/sample_industry_consultants.xlsx
+++ b/sample-uploads/sample_industry_consultants.xlsx
@@ -397,19 +397,22 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:D6"/>
+  <dimension ref="A1:E7"/>
   <sheetData>
     <row r="1">
       <c r="A1" t="str">
         <v>Name</v>
       </c>
       <c r="B1" t="str">
+        <v>Email</v>
+      </c>
+      <c r="C1" t="str">
         <v>Company</v>
       </c>
-      <c r="C1" t="str">
+      <c r="D1" t="str">
         <v>Expertise</v>
       </c>
-      <c r="D1" t="str">
+      <c r="E1" t="str">
         <v>Assigned Course</v>
       </c>
     </row>
@@ -418,12 +421,15 @@
         <v>Engr. Paolo Mendoza</v>
       </c>
       <c r="B2" t="str">
+        <v>paolo.mendoza@unc.edu.ph</v>
+      </c>
+      <c r="C2" t="str">
         <v>Accenture Philippines</v>
       </c>
-      <c r="C2" t="str">
+      <c r="D2" t="str">
         <v>Cybersecurity</v>
       </c>
-      <c r="D2" t="str">
+      <c r="E2" t="str">
         <v>BIT304</v>
       </c>
     </row>
@@ -432,12 +438,15 @@
         <v>Ms. Andrea Villanueva</v>
       </c>
       <c r="B3" t="str">
+        <v>andrea.villanueva@unc.edu.ph</v>
+      </c>
+      <c r="C3" t="str">
         <v>Globe Telecom</v>
       </c>
-      <c r="C3" t="str">
+      <c r="D3" t="str">
         <v>Web &amp; Cloud</v>
       </c>
-      <c r="D3" t="str">
+      <c r="E3" t="str">
         <v>BIT301</v>
       </c>
     </row>
@@ -446,12 +455,15 @@
         <v>Mr. Carlo Tan</v>
       </c>
       <c r="B4" t="str">
+        <v>carlo.tan@unc.edu.ph</v>
+      </c>
+      <c r="C4" t="str">
         <v>Canva</v>
       </c>
-      <c r="C4" t="str">
+      <c r="D4" t="str">
         <v>UX / Product Design</v>
       </c>
-      <c r="D4" t="str">
+      <c r="E4" t="str">
         <v>BIT313L</v>
       </c>
     </row>
@@ -460,12 +472,15 @@
         <v>Dr. Liza Fernandez</v>
       </c>
       <c r="B5" t="str">
+        <v>liza.fernandez@unc.edu.ph</v>
+      </c>
+      <c r="C5" t="str">
         <v>DOST-ASTI</v>
       </c>
-      <c r="C5" t="str">
+      <c r="D5" t="str">
         <v>Software Engineering</v>
       </c>
-      <c r="D5" t="str">
+      <c r="E5" t="str">
         <v>BIT303; BIT401</v>
       </c>
     </row>
@@ -474,18 +489,38 @@
         <v>Mr. Rafael Ong</v>
       </c>
       <c r="B6" t="str">
+        <v>rafael.ong@unc.edu.ph</v>
+      </c>
+      <c r="C6" t="str">
         <v>Oracle Philippines</v>
       </c>
-      <c r="C6" t="str">
+      <c r="D6" t="str">
         <v>Databases</v>
       </c>
-      <c r="D6" t="str">
+      <c r="E6" t="str">
         <v>BIT201</v>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="str">
+        <v>Roberto Cruz</v>
+      </c>
+      <c r="B7" t="str">
+        <v>roberto.cruz@unc.edu.ph</v>
+      </c>
+      <c r="C7" t="str">
+        <v>Smart Communications</v>
+      </c>
+      <c r="D7" t="str">
+        <v>Full-Stack Development</v>
+      </c>
+      <c r="E7" t="str">
+        <v>BIT302</v>
       </c>
     </row>
   </sheetData>
   <ignoredErrors>
-    <ignoredError numberStoredAsText="1" sqref="A1:D6"/>
+    <ignoredError numberStoredAsText="1" sqref="A1:E7"/>
   </ignoredErrors>
 </worksheet>
 </file>